--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2019_biobio.xlsx
@@ -555,7 +555,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:29</t>
+    <t xml:space="preserve">2026-09-18 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2019_biobio.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">62</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">24</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Tirúa</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">287</t>
@@ -555,7 +555,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:09</t>
+    <t xml:space="preserve">2026-10-05 04:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
